--- a/Clean Bond Prices and yeilds to maturity Calculator.xlsx
+++ b/Clean Bond Prices and yeilds to maturity Calculator.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29518"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D8851FD-69BA-4A2E-8078-1912562440DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2445F2F5-DEC3-45D4-A476-E7D927CD4E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Calculator " sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -75,14 +75,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -101,8 +100,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -110,19 +121,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -470,17 +498,17 @@
   </cols>
   <sheetData>
     <row r="7" spans="1:4">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="4">
         <v>0.11</v>
       </c>
     </row>
@@ -499,90 +527,90 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12">
+      <c r="A12" s="3">
         <v>0.5</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="3">
         <v>5</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="3">
         <f>1/((1+B$9)^A12)</f>
         <v>0.94915799575249904</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="3">
         <f>$B12*$C12</f>
         <v>4.7457899787624953</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13">
+      <c r="A13" s="3">
         <v>1.5</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="3">
         <v>5</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="3">
         <f>1/((1+B$9)^A13)</f>
         <v>0.85509729347071961</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="3">
         <f>$B13*$C13</f>
         <v>4.2754864673535984</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14">
+      <c r="A14" s="3">
         <v>2.5</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="3">
         <v>5</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="3">
         <f>1/((1+B$9)^A14)</f>
         <v>0.77035792204569342</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="3">
         <f>$B14*$C14</f>
         <v>3.851789610228467</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15">
+      <c r="A15" s="3">
         <v>3.5</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="3">
         <v>5</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="3">
         <f>1/((1+B$9)^A15)</f>
         <v>0.69401614598711103</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="3">
         <f>$B15*$C15</f>
         <v>3.4700807299355549</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16">
+      <c r="A16" s="3">
         <v>4.5</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="3">
         <v>105</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="3">
         <f>1/((1+B$9)^A16)</f>
         <v>0.62523977115955953</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="3">
         <f>$B16*$C16</f>
         <v>65.650175971753754</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="5">
         <f>SUM(D12:D16)</f>
         <v>81.993322758033869</v>
       </c>
